--- a/sample-files/AgencyB_Submissions.xlsx
+++ b/sample-files/AgencyB_Submissions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,9 +633,9 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Scar / birthmark</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Face/neck tattoos</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ponytail</t>
+          <t>Hat</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -783,40 +783,129 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Sara Iqbal</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sara@example.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1992-04</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Glasses, Hat</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Makeup; Earrings</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tom Ellis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tom@example.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1987-10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>35-44</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Glasses; Sombrero</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Ana Reyes</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>ana@example.com</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>1990/05</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>25-34</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Short hair</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Glasses</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
